--- a/grupos/4BLCM - Estadisticos 20232.xlsx
+++ b/grupos/4BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Hernández Castro Enrique</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -233,22 +233,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>MELISA VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -775,25 +766,25 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -823,10 +814,10 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -835,7 +826,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -864,25 +855,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -912,10 +903,10 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -953,25 +944,25 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1001,19 +992,19 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1042,25 +1033,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1087,19 +1078,19 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1131,25 +1122,25 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1176,13 +1167,13 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1220,25 +1211,25 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1309,25 +1300,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1357,10 +1348,10 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1398,25 +1389,25 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1440,17 +1431,17 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
+        <v>9</v>
+      </c>
+      <c r="Z11">
         <v>7</v>
       </c>
-      <c r="Z11">
-        <v>8</v>
-      </c>
       <c r="AA11">
         <v>8</v>
       </c>
@@ -1458,7 +1449,7 @@
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1487,25 +1478,25 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1529,13 +1520,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1547,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1576,25 +1567,25 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1624,10 +1615,10 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1636,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1665,25 +1656,25 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1710,13 +1701,13 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1754,25 +1745,25 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1843,25 +1834,25 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1932,25 +1923,25 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1986,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2021,25 +2012,25 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2069,16 +2060,16 @@
         <v>9</v>
       </c>
       <c r="Y18">
+        <v>9</v>
+      </c>
+      <c r="Z18">
         <v>7</v>
       </c>
-      <c r="Z18">
-        <v>8</v>
-      </c>
       <c r="AA18">
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>10</v>
@@ -2110,25 +2101,25 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2170,7 +2161,7 @@
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2199,25 +2190,25 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2288,25 +2279,25 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2333,13 +2324,13 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21">
         <v>10</v>
@@ -2377,25 +2368,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2466,25 +2457,25 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2555,25 +2546,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2606,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -2644,25 +2635,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2692,10 +2683,10 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2733,25 +2724,25 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2775,25 +2766,25 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2822,25 +2813,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2867,13 +2858,13 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -2911,25 +2902,25 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3000,25 +2991,25 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3048,16 +3039,16 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>10</v>
@@ -3089,25 +3080,25 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3137,7 +3128,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3149,7 +3140,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3178,25 +3169,25 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3220,25 +3211,25 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3267,25 +3258,25 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3312,10 +3303,10 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>7</v>
@@ -3324,7 +3315,7 @@
         <v>10</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC32">
         <v>10</v>
@@ -3356,25 +3347,25 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3401,22 +3392,22 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3445,25 +3436,25 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3490,19 +3481,19 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34">
         <v>9</v>
       </c>
       <c r="AB34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC34">
         <v>10</v>
@@ -3534,25 +3525,25 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3576,16 +3567,16 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35">
         <v>8</v>
@@ -3623,25 +3614,25 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3665,16 +3656,16 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA36">
         <v>10</v>
@@ -3712,25 +3703,25 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3757,13 +3748,13 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA37">
         <v>10</v>
@@ -3801,25 +3792,25 @@
         <v>8</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3849,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z38">
         <v>7</v>
@@ -3858,10 +3849,10 @@
         <v>8</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC38">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -3890,25 +3881,25 @@
         <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3979,25 +3970,25 @@
         <v>7</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4021,25 +4012,25 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z40">
         <v>7</v>
       </c>
       <c r="AA40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB40">
         <v>7</v>
       </c>
       <c r="AC40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4068,25 +4059,25 @@
         <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4113,13 +4104,13 @@
         <v>10</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA41">
         <v>10</v>
@@ -4128,7 +4119,7 @@
         <v>10</v>
       </c>
       <c r="AC41">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5163,43 +5154,43 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="L17">
-        <v>31.3</v>
+        <v>15.6</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="Q17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="S17">
-        <v>31.3</v>
+        <v>15.6</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -6727,7 +6718,7 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -6739,7 +6730,7 @@
         <v>100</v>
       </c>
       <c r="M40">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N40">
         <v>100</v>
@@ -6748,7 +6739,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6760,7 +6751,7 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="U40">
         <v>100</v>
@@ -6891,7 +6882,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6900,19 +6891,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>89.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6926,25 +6917,25 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3">
         <v>38</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="G3" s="2">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6958,7 +6949,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>38</v>
@@ -6976,7 +6967,7 @@
         <v>5.3</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6987,10 +6978,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>38</v>
@@ -7008,7 +6999,7 @@
         <v>5.3</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7019,7 +7010,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -7028,16 +7019,16 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="G6" s="2">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -7051,7 +7042,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -7060,19 +7051,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="G7" s="2">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7083,7 +7074,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -7104,7 +7095,7 @@
         <v>2.6</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7154,7 +7145,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7186,70 +7177,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920176</v>
+        <v>22330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
         <v>73</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920176</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920144</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BLCM - Estadisticos 20232.xlsx
+++ b/grupos/4BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -209,13 +209,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Hernández Castro Enrique</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
   </si>
   <si>
     <t>Faltante Faltante Faltante</t>
@@ -231,15 +231,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -787,46 +778,46 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -876,25 +867,25 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -903,7 +894,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>8</v>
@@ -912,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -965,31 +956,31 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -998,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>8</v>
@@ -1054,31 +1045,31 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1143,25 +1134,25 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1179,10 +1170,10 @@
         <v>10</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1232,25 +1223,25 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1268,7 +1259,7 @@
         <v>10</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1321,25 +1312,25 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1357,7 +1348,7 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1410,46 +1401,46 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1499,25 +1490,25 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1526,13 +1517,13 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1588,25 +1579,25 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1615,19 +1606,19 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1677,34 +1668,34 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1713,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>10</v>
@@ -1766,25 +1757,25 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1855,25 +1846,25 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1891,7 +1882,7 @@
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -1944,25 +1935,25 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -1977,7 +1968,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2033,25 +2024,25 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2063,7 +2054,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2072,7 +2063,7 @@
         <v>9</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2122,31 +2113,31 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2155,13 +2146,13 @@
         <v>10</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2211,25 +2202,25 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2300,31 +2291,31 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2336,7 +2327,7 @@
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>10</v>
@@ -2389,25 +2380,25 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2478,25 +2469,25 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2567,25 +2558,25 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2603,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -2656,25 +2647,25 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2692,10 +2683,10 @@
         <v>10</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2745,25 +2736,25 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2772,13 +2763,13 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>9</v>
@@ -2834,31 +2825,31 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2870,10 +2861,10 @@
         <v>10</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2923,25 +2914,25 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3012,28 +3003,28 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3042,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>9</v>
@@ -3051,7 +3042,7 @@
         <v>9</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3101,46 +3092,46 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3190,25 +3181,25 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3229,7 +3220,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3264,7 +3255,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -3279,34 +3270,34 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>7</v>
@@ -3318,7 +3309,7 @@
         <v>9</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3368,34 +3359,34 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z33">
         <v>9</v>
@@ -3407,7 +3398,7 @@
         <v>9</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3457,37 +3448,37 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>9</v>
@@ -3496,7 +3487,7 @@
         <v>9</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3546,28 +3537,28 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3579,13 +3570,13 @@
         <v>10</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB35">
         <v>8</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3635,46 +3626,46 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA36">
         <v>10</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3724,25 +3715,25 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3760,7 +3751,7 @@
         <v>10</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>10</v>
@@ -3813,25 +3804,25 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3846,7 +3837,7 @@
         <v>7</v>
       </c>
       <c r="AA38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB38">
         <v>9</v>
@@ -3902,25 +3893,25 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -3938,7 +3929,7 @@
         <v>10</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC39">
         <v>10</v>
@@ -3991,28 +3982,28 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -4024,7 +4015,7 @@
         <v>7</v>
       </c>
       <c r="AA40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB40">
         <v>7</v>
@@ -4080,34 +4071,34 @@
         <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z41">
         <v>8</v>
@@ -4116,7 +4107,7 @@
         <v>10</v>
       </c>
       <c r="AB41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC41">
         <v>9</v>
@@ -5175,22 +5166,22 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>50</v>
+        <v>34.4</v>
       </c>
       <c r="Q17">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="R17">
-        <v>50</v>
+        <v>34.4</v>
       </c>
       <c r="S17">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="T17">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="U17">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5935,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -6739,7 +6730,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6751,7 +6742,7 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U40">
         <v>100</v>
@@ -6882,7 +6873,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6891,19 +6882,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="G2" s="2">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6914,7 +6905,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6935,7 +6926,7 @@
         <v>5.3</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6946,10 +6937,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>38</v>
@@ -6978,10 +6969,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>38</v>
@@ -6999,7 +6990,7 @@
         <v>5.3</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7010,7 +7001,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -7031,7 +7022,7 @@
         <v>5.3</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7042,7 +7033,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -7063,7 +7054,7 @@
         <v>5.3</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7074,7 +7065,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -7083,19 +7074,19 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="G8" s="2">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7145,7 +7136,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7175,29 +7166,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920145</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
